--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -528,6 +528,9 @@
       <c r="C11" t="str">
         <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -586,7 +589,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0209535302520510300</v>
+        <v>02095353025205103015</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -490,6 +490,9 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="str">
+        <v>4</v>
+      </c>
       <c r="C7" t="str">
         <v>572_乒乓菊白_undefined_undefined_1bunch</v>
       </c>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -510,7 +510,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="str">
         <v>572_乒乓菊白_undefined_undefined_1bunch</v>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -535,9 +535,97 @@
         <v>15</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>6</v>
+      </c>
+      <c r="C12" t="str">
+        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="C13" t="str" xml:space="preserve">
+        <v xml:space="preserve">416_翠珠紫_Didiscus caeruleus
+blue_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="C14" t="str" xml:space="preserve">
+        <v xml:space="preserve">497_小飞燕粉色_delphinium ballkleid
+pink_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="C15" t="str" xml:space="preserve">
+        <v xml:space="preserve">405_小飞燕深蓝_ delphinium ballkleid
+dark blue_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="C16" t="str" xml:space="preserve">
+        <v xml:space="preserve">404_小飞燕白色_ delphinium ballkleid
+white_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="C17" t="str" xml:space="preserve">
+        <v xml:space="preserve">499_小飞燕浅蓝_delphinium ballkleid
+light blue_undefined_1bunch</v>
+      </c>
+      <c r="F17" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>496_大飞燕深蓝色_delphinium dark blue_undefined_1bunch</v>
+      </c>
+      <c r="F18" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>578_腊梅粉_wax pink_undefined_1bunch</v>
+      </c>
+      <c r="F19" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>7</v>
+      </c>
+      <c r="C20" t="str">
+        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -592,7 +680,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02095353025205103015</v>
+        <v>020953530252051030155015202020203025300</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -622,6 +622,9 @@
       <c r="C21" t="str">
         <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -680,7 +683,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020953530252051030155015202020203025300</v>
+        <v>0209535302520510301550152020202030253030</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -626,9 +626,92 @@
         <v>30</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>578_腊梅粉_wax pink_undefined_1bunch</v>
+      </c>
+      <c r="F22" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>577_腊梅白_wax white_undefined_1bunch</v>
+      </c>
+      <c r="F23" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>865_腊梅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F24" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>8</v>
+      </c>
+      <c r="C25" t="str">
+        <v>521_商陆_phytolacca acinosa _undefined_1bunch</v>
+      </c>
+      <c r="F25" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>318_尤加利果_Eucalyptus pods_undefined_1bunch</v>
+      </c>
+      <c r="F26" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>579_腊梅红_wax red_undefined_1bunch</v>
+      </c>
+      <c r="F27" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>9</v>
+      </c>
+      <c r="C28" t="str">
+        <v>576_迷你菊紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F28" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>576_迷你菊紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F29" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>575_迷你菊深粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F30" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -683,7 +766,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0209535302520510301550152020202030253030</v>
+        <v>02095353025205103015501520202020302530303050135017255020500</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -708,10 +708,97 @@
       <c r="A31" t="str">
         <v>10</v>
       </c>
+      <c r="C31" t="str">
+        <v>574_迷你菊白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F31" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>846_玛格丽特_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>579_腊梅红_wax red_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>11</v>
+      </c>
+      <c r="C34" t="str">
+        <v>548_白星花_tweedia white_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="C35" t="str" xml:space="preserve">
+        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
+white_Trachymene Coerulea_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>530_蔷薇果_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="str">
+        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>421_松虫草黑色_scabiosa black_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -766,7 +853,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02095353025205103015501520202020302530303050135017255020500</v>
+        <v>02095353025205103015501520202020302530303050135017255020505050253052015305300</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -795,6 +795,9 @@
       <c r="C41" t="str">
         <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -853,7 +856,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02095353025205103015501520202020302530303050135017255020505050253052015305300</v>
+        <v>020953530252051030155015202020203025303030501350172550205050502530520153053013</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -799,9 +799,98 @@
         <v>13</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>12</v>
+      </c>
+      <c r="C42" t="str">
+        <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F43" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F44" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>13</v>
+      </c>
+      <c r="C45" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F45" t="str">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F46" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>14</v>
+      </c>
+      <c r="C47" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F47" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>318_尤加利果_Eucalyptus pods_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
+      </c>
+      <c r="F50" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -856,7 +945,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020953530252051030155015202020203025303030501350172550205050502530520153053013</v>
+        <v>02095353025205103015501520202020302530303050135017255020505050253052015305301321501060404010153030</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -888,9 +888,98 @@
         <v>30</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>15</v>
+      </c>
+      <c r="C52" t="str">
+        <v>328_卢荀草_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>551_铁线莲_Glematis_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v/>
+      </c>
+      <c r="C56" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>16</v>
+      </c>
+      <c r="C57" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>17</v>
+      </c>
+      <c r="C58" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F59" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>590_洋牡丹粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F60" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>586_洋牡丹白_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -945,7 +1034,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02095353025205103015501520202020302530303050135017255020505050253052015305301321501060404010153030</v>
+        <v>02095353025205103015501520202020302530303050135017255020505050253052015305301321501060404010153030302830427421530500</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -976,6 +976,9 @@
       <c r="C61" t="str">
         <v>586_洋牡丹白_undefined_undefined_1bunch</v>
       </c>
+      <c r="F61" t="str">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1034,7 +1037,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02095353025205103015501520202020302530303050135017255020505050253052015305301321501060404010153030302830427421530500</v>
+        <v>0209535302520510301550152020202030253030305013501725502050505025305201530530132150106040401015303030283042742153050100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -980,9 +980,44 @@
         <v>100</v>
       </c>
     </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>589_洋牡丹香槟_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>18</v>
+      </c>
+      <c r="C63" t="str">
+        <v>589_洋牡丹香槟_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F63" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="str">
+        <v>588_洋牡丹黄_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>676_洋牡丹玫红_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L65"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1037,7 +1072,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0209535302520510301550152020202030253030305013501725502050505025305201530530132150106040401015303030283042742153050100</v>
+        <v>020953530252051030155015202020203025303030501350172550205050502530520153053013215010604040101530303028304274215305010029293034</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,581 +443,93 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>780_贝壳草_undefined_undefined_1bunch</v>
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F2" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F3" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2</v>
+      </c>
+      <c r="C4" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F4" t="str">
         <v>20</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="C3" t="str" xml:space="preserve">
-        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
-white_Trachymene Coerulea_1bunch</v>
-      </c>
-      <c r="F3" t="str">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
-      <c r="C4" t="str" xml:space="preserve">
-        <v xml:space="preserve">416_翠珠紫_Didiscus caeruleus
-blue_Trachymene Coerulea_1bunch</v>
-      </c>
-      <c r="F4" t="str">
-        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="str">
-        <v>558_油画小菊_Helenium_undefined_1bunch</v>
+        <v>211_海洋之心_Nautica_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F5" t="str">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>3</v>
-      </c>
       <c r="C6" t="str">
-        <v>573_乒乓菊粉_undefined_undefined_1bunch</v>
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F6" t="str">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" t="str">
-        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F7" t="str">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="str">
-        <v>573_乒乓菊粉_undefined_undefined_1bunch</v>
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F8" t="str">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="str">
-        <v>572_乒乓菊白_undefined_undefined_1bunch</v>
+        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F9" t="str">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" t="str">
-        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F10" t="str">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="str">
-        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
-      </c>
-      <c r="F11" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>6</v>
-      </c>
-      <c r="C12" t="str">
-        <v>454_蓝星花_tweedia blue_undefined_1bunch</v>
-      </c>
-      <c r="F12" t="str">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
-      <c r="C13" t="str" xml:space="preserve">
-        <v xml:space="preserve">416_翠珠紫_Didiscus caeruleus
-blue_Trachymene Coerulea_1bunch</v>
-      </c>
-      <c r="F13" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="C14" t="str" xml:space="preserve">
-        <v xml:space="preserve">497_小飞燕粉色_delphinium ballkleid
-pink_undefined_1bunch</v>
-      </c>
-      <c r="F14" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="C15" t="str" xml:space="preserve">
-        <v xml:space="preserve">405_小飞燕深蓝_ delphinium ballkleid
-dark blue_undefined_1bunch</v>
-      </c>
-      <c r="F15" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" xml:space="preserve">
-      <c r="C16" t="str" xml:space="preserve">
-        <v xml:space="preserve">404_小飞燕白色_ delphinium ballkleid
-white_undefined_1bunch</v>
-      </c>
-      <c r="F16" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
-      <c r="C17" t="str" xml:space="preserve">
-        <v xml:space="preserve">499_小飞燕浅蓝_delphinium ballkleid
-light blue_undefined_1bunch</v>
-      </c>
-      <c r="F17" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="str">
-        <v>496_大飞燕深蓝色_delphinium dark blue_undefined_1bunch</v>
-      </c>
-      <c r="F18" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="str">
-        <v>578_腊梅粉_wax pink_undefined_1bunch</v>
-      </c>
-      <c r="F19" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>7</v>
-      </c>
-      <c r="C20" t="str">
-        <v>403_大飞燕浅蓝色_delphinium light blue_undefined_1bunch</v>
-      </c>
-      <c r="F20" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="str">
-        <v>401_大飞燕白色_delphinium white_undefined_1bunch</v>
-      </c>
-      <c r="F21" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="str">
-        <v>578_腊梅粉_wax pink_undefined_1bunch</v>
-      </c>
-      <c r="F22" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="str">
-        <v>577_腊梅白_wax white_undefined_1bunch</v>
-      </c>
-      <c r="F23" t="str">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="str">
-        <v>865_腊梅紫_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F24" t="str">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>8</v>
-      </c>
-      <c r="C25" t="str">
-        <v>521_商陆_phytolacca acinosa _undefined_1bunch</v>
-      </c>
-      <c r="F25" t="str">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="str">
-        <v>318_尤加利果_Eucalyptus pods_undefined_1bunch</v>
-      </c>
-      <c r="F26" t="str">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="str">
-        <v>579_腊梅红_wax red_undefined_1bunch</v>
-      </c>
-      <c r="F27" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>9</v>
-      </c>
-      <c r="C28" t="str">
-        <v>576_迷你菊紫_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F28" t="str">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="str">
-        <v>576_迷你菊紫_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F29" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="str">
-        <v>575_迷你菊深粉_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F30" t="str">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>10</v>
-      </c>
-      <c r="C31" t="str">
-        <v>574_迷你菊白_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F31" t="str">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="str">
-        <v>846_玛格丽特_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F32" t="str">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="str">
-        <v>579_腊梅红_wax red_undefined_1bunch</v>
-      </c>
-      <c r="F33" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>11</v>
-      </c>
-      <c r="C34" t="str">
-        <v>548_白星花_tweedia white_undefined_1bunch</v>
-      </c>
-      <c r="F34" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
-      <c r="C35" t="str" xml:space="preserve">
-        <v xml:space="preserve">510_翠珠白_Didiscus caeruleus 
-white_Trachymene Coerulea_1bunch</v>
-      </c>
-      <c r="F35" t="str">
+      <c r="A11" t="str">
         <v>5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="str">
-        <v>530_蔷薇果_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F36" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="str">
-        <v>419_松虫草红_scabiosa watermelon_undefined_1bunch</v>
-      </c>
-      <c r="F37" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="str">
-        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
-      </c>
-      <c r="F38" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="str">
-        <v>421_松虫草黑色_scabiosa black_undefined_1bunch</v>
-      </c>
-      <c r="F39" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="str">
-        <v>878_玛格丽特粉_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F40" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="str">
-        <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F41" t="str">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>12</v>
-      </c>
-      <c r="C42" t="str">
-        <v>237_酷皮_Kupi_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F42" t="str">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="str">
-        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
-      </c>
-      <c r="F43" t="str">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="str">
-        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
-      </c>
-      <c r="F44" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>13</v>
-      </c>
-      <c r="C45" t="str">
-        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
-      </c>
-      <c r="F45" t="str">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="str">
-        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
-      </c>
-      <c r="F46" t="str">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>14</v>
-      </c>
-      <c r="C47" t="str">
-        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
-      </c>
-      <c r="F47" t="str">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="str">
-        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F48" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="str">
-        <v>318_尤加利果_Eucalyptus pods_undefined_1bunch</v>
-      </c>
-      <c r="F49" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="str">
-        <v>456_蕾丝白色_lace flower white_undefined_1bunch</v>
-      </c>
-      <c r="F50" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="str">
-        <v>49_亚丁_Pasta Rosata_Gerbera L._10stems</v>
-      </c>
-      <c r="F51" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>15</v>
-      </c>
-      <c r="C52" t="str">
-        <v>328_卢荀草_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F52" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="str">
-        <v>484_天鹅绒_Star of Bethlehem_undefined_1bunch</v>
-      </c>
-      <c r="F53" t="str">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" t="str">
-        <v>551_铁线莲_Glematis_undefined_1bunch</v>
-      </c>
-      <c r="F54" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="str">
-        <v>880_铁线莲浅紫_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F55" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v/>
-      </c>
-      <c r="C56" t="str">
-        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F56" t="str">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>16</v>
-      </c>
-      <c r="C57" t="str">
-        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F57" t="str">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>17</v>
-      </c>
-      <c r="C58" t="str">
-        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F58" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" t="str">
-        <v>585_洋牡丹红_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F59" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="C60" t="str">
-        <v>590_洋牡丹粉_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F60" t="str">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="C61" t="str">
-        <v>586_洋牡丹白_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F61" t="str">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="C62" t="str">
-        <v>589_洋牡丹香槟_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F62" t="str">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>18</v>
-      </c>
-      <c r="C63" t="str">
-        <v>589_洋牡丹香槟_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F63" t="str">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="C64" t="str">
-        <v>588_洋牡丹黄_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F64" t="str">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="C65" t="str">
-        <v>676_洋牡丹玫红_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F65" t="str">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1072,7 +584,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020953530252051030155015202020203025303030501350172550205050502530520153053013215010604040101530303028304274215305010029293034</v>
+        <v>030142014103093640</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -526,6 +526,9 @@
       <c r="A11" t="str">
         <v>5</v>
       </c>
+      <c r="C11" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -529,6 +529,9 @@
       <c r="C11" t="str">
         <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -587,7 +590,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030142014103093640</v>
+        <v>0301420141030936416</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -533,9 +533,95 @@
         <v>16</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>261_单头蓝莓_Blueberry_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>6</v>
+      </c>
+      <c r="C14" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>705_中华桔梗紫_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>7</v>
+      </c>
+      <c r="C17" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>8</v>
+      </c>
+      <c r="C20" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="str">
+        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -590,7 +676,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0301420141030936416</v>
+        <v>0301420141030936416162220.5182011229250</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -618,6 +618,9 @@
       <c r="C21" t="str">
         <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -676,7 +679,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0301420141030936416162220.5182011229250</v>
+        <v>0301420141030936416162220.51820112292524</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -622,9 +622,95 @@
         <v>24</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>9</v>
+      </c>
+      <c r="C22" t="str">
+        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>10</v>
+      </c>
+      <c r="C25" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>11</v>
+      </c>
+      <c r="C28" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F29" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F30" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -679,7 +765,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0301420141030936416162220.51820112292524</v>
+        <v>0301420141030936416162220.51820112292524159.516142086780</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -707,6 +707,9 @@
       <c r="C31" t="str">
         <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F31" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -765,7 +768,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0301420141030936416162220.51820112292524159.516142086780</v>
+        <v>0301420141030936416162220.51820112292524159.516142086781</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -708,12 +708,101 @@
         <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F31" t="str">
-        <v>1</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F32" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F33" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>12</v>
+      </c>
+      <c r="C34" t="str">
+        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F34" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v/>
+      </c>
+      <c r="C35" t="str">
+        <v>246_多头蓝莓_Blueberry Spray_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F35" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>13</v>
+      </c>
+      <c r="C37" t="str">
+        <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F37" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F38" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>14</v>
+      </c>
+      <c r="C40" t="str">
+        <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -768,7 +857,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0301420141030936416162220.51820112292524159.516142086781</v>
+        <v>0301420141030936416162220.51820112292524159.5161420867818152292015201616240</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -799,6 +799,9 @@
       <c r="C41" t="str">
         <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -857,7 +860,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0301420141030936416162220.51820112292524159.5161420867818152292015201616240</v>
+        <v>0301420141030936416162220.51820112292524159.5161420867818152292015201616241</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -800,12 +800,95 @@
         <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F41" t="str">
-        <v>1</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>15</v>
+      </c>
+      <c r="C42" t="str">
+        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F42" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>211_海洋之心_Nautica_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>16</v>
+      </c>
+      <c r="C45" t="str">
+        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>261_单头蓝莓_Blueberry_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -860,7 +943,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0301420141030936416162220.51820112292524159.5161420867818152292015201616241</v>
+        <v>0301420141030936416162220.51820112292524159.5161420867818152292015201616241426975176127150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -885,10 +885,102 @@
       <c r="C51" t="str">
         <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F51" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>17</v>
+      </c>
+      <c r="C52" t="str">
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="str">
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="C54" t="str" xml:space="preserve">
+        <v xml:space="preserve">413_风铃花淡紫色_Canterbury Bells
+light purple_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" xml:space="preserve">
+      <c r="C55" t="str" xml:space="preserve">
+        <v xml:space="preserve">508_风铃花白色_Canterbury Bells 
+white_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
+      <c r="C56" t="str" xml:space="preserve">
+        <v xml:space="preserve">414_风铃花粉色_Canterbury Bells
+pink_undefined_1bunch</v>
+      </c>
+      <c r="F56" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>582_腊梅蓝_wax blue_undefined_1bunch</v>
+      </c>
+      <c r="F57" t="str">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>18</v>
+      </c>
+      <c r="C58" t="str">
+        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F58" t="str">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F59" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>19</v>
+      </c>
+      <c r="C60" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F60" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -943,7 +1035,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0301420141030936416162220.51820112292524159.5161420867818152292015201616241426975176127150</v>
+        <v>0301420141030936416162220.51820112292524159.5161420867818152292015201616241426975176127154320202525453110200</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -977,10 +977,24 @@
       <c r="C61" t="str">
         <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F61" t="str">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>20</v>
+      </c>
+      <c r="C62" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F62" t="str">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L62"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1035,7 +1049,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0301420141030936416162220.51820112292524159.5161420867818152292015201616241426975176127154320202525453110200</v>
+        <v>0301420141030936416162220.51820112292524159.5161420867818152292015201616241426975176127154320202525453110201911</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -440,10 +440,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C2" t="str">
-        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F2" t="str">
         <v>30</v>
@@ -451,550 +451,82 @@
     </row>
     <row r="3">
       <c r="C3" t="str">
-        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F3" t="str">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>2</v>
-      </c>
       <c r="C4" t="str">
-        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F4" t="str">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="str">
+        <v>21</v>
+      </c>
       <c r="C5" t="str">
-        <v>211_海洋之心_Nautica_Rosa rugosa Thunb._20stems</v>
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F5" t="str">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="C6" t="str">
-        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F6" t="str">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>3</v>
-      </c>
       <c r="C7" t="str">
-        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F7" t="str">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" t="str">
-        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F8" t="str">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C9" t="str">
-        <v>208_紫霞仙子 _Nightingale_Rosa rugosa Thunb._20stems</v>
+        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F9" t="str">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" t="str">
-        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
       </c>
       <c r="F10" t="str">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>5</v>
-      </c>
       <c r="C11" t="str">
-        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F11" t="str">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="C12" t="str">
-        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F12" t="str">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="C13" t="str">
-        <v>261_单头蓝莓_Blueberry_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F13" t="str">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>6</v>
-      </c>
-      <c r="C14" t="str">
-        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F14" t="str">
-        <v>20.5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="C15" t="str">
-        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F15" t="str">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="C16" t="str">
-        <v>705_中华桔梗紫_undefined_undefined_1bunch</v>
-      </c>
-      <c r="F16" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>7</v>
-      </c>
-      <c r="C17" t="str">
-        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F17" t="str">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="C18" t="str">
-        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F18" t="str">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="C19" t="str">
-        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F19" t="str">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>8</v>
-      </c>
-      <c r="C20" t="str">
-        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F20" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="str">
-        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F21" t="str">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>9</v>
-      </c>
-      <c r="C22" t="str">
-        <v>273_蓝调_bluetone_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F22" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="str">
-        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F23" t="str">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="str">
-        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F24" t="str">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>10</v>
-      </c>
-      <c r="C25" t="str">
-        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F25" t="str">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="str">
-        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F26" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="str">
-        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F27" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>11</v>
-      </c>
-      <c r="C28" t="str">
-        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F28" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="str">
-        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F29" t="str">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="str">
-        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F30" t="str">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="str">
-        <v>285_多头紫罗兰_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F31" t="str">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="str">
-        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F32" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="str">
-        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F33" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>12</v>
-      </c>
-      <c r="C34" t="str">
-        <v>286_红蕾丝_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F34" t="str">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v/>
-      </c>
-      <c r="C35" t="str">
-        <v>246_多头蓝莓_Blueberry Spray_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F35" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="str">
-        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F36" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>13</v>
-      </c>
-      <c r="C37" t="str">
-        <v>281_莱拉_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F37" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="str">
-        <v>177_国王日_Kings Day_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F38" t="str">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="C39" t="str">
-        <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F39" t="str">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>14</v>
-      </c>
-      <c r="C40" t="str">
-        <v>138_卡罗拉_Carola_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F40" t="str">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="str">
-        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F41" t="str">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>15</v>
-      </c>
-      <c r="C42" t="str">
-        <v>197_粉红雪山_Sweet Avalanche_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F42" t="str">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="str">
-        <v>211_海洋之心_Nautica_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F43" t="str">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="str">
-        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F44" t="str">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>16</v>
-      </c>
-      <c r="C45" t="str">
-        <v>181_月光女神_undefined_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F45" t="str">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="str">
-        <v>261_单头蓝莓_Blueberry_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F46" t="str">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="str">
-        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F47" t="str">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="str">
-        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F48" t="str">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="str">
-        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F49" t="str">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="str">
-        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F50" t="str">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="str">
-        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F51" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>17</v>
-      </c>
-      <c r="C52" t="str">
-        <v>268_猩红泡泡_spray red_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F52" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="str">
-        <v>221_朱丽叶塔_Julieta_Rosa rugosa Thunb._10stems</v>
-      </c>
-      <c r="F53" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" xml:space="preserve">
-      <c r="C54" t="str" xml:space="preserve">
-        <v xml:space="preserve">413_风铃花淡紫色_Canterbury Bells
-light purple_undefined_1bunch</v>
-      </c>
-      <c r="F54" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" xml:space="preserve">
-      <c r="C55" t="str" xml:space="preserve">
-        <v xml:space="preserve">508_风铃花白色_Canterbury Bells 
-white_undefined_1bunch</v>
-      </c>
-      <c r="F55" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="56" xml:space="preserve">
-      <c r="C56" t="str" xml:space="preserve">
-        <v xml:space="preserve">414_风铃花粉色_Canterbury Bells
-pink_undefined_1bunch</v>
-      </c>
-      <c r="F56" t="str">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" t="str">
-        <v>582_腊梅蓝_wax blue_undefined_1bunch</v>
-      </c>
-      <c r="F57" t="str">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>18</v>
-      </c>
-      <c r="C58" t="str">
-        <v>193_粉爱神_Pink Cupid_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F58" t="str">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" t="str">
-        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F59" t="str">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>19</v>
-      </c>
-      <c r="C60" t="str">
-        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F60" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="C61" t="str">
-        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F61" t="str">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>20</v>
-      </c>
-      <c r="C62" t="str">
-        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
-      </c>
-      <c r="F62" t="str">
-        <v>11</v>
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1049,7 +581,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0301420141030936416162220.51820112292524159.5161420867818152292015201616241426975176127154320202525453110201911</v>
+        <v>030410313331510250</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -523,6 +523,9 @@
       <c r="C11" t="str">
         <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -581,7 +584,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030410313331510250</v>
+        <v>030410313331510255</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-13.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-13.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -527,9 +527,71 @@
         <v>5</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>224_折射_Reflex_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>23</v>
+      </c>
+      <c r="C13" t="str">
+        <v>648_洋牡丹河内_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>24</v>
+      </c>
+      <c r="C15" t="str">
+        <v>649_洋牡丹樱花粉_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -584,7 +646,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>030410313331510255</v>
+        <v>0304103133315102558501040111</v>
       </c>
     </row>
   </sheetData>
